--- a/src/main/resources/git.xlsx
+++ b/src/main/resources/git.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9F1D2C-053A-47D5-BEDF-3A8D54CAE60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE9C6B3-18B9-3B40-9392-E76A8476CE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6940" yWindow="780" windowWidth="23260" windowHeight="12580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,16 +14,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$38</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t>lcpt-dxfund</t>
   </si>
@@ -295,6 +290,43 @@
   </si>
   <si>
     <t>console-dxasset-vue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>console-fina-vue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.hundsun.com/ifms6.0/fina/HUI1.0-console-fina.git</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lcpt-fina</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.hundsun.com/ifms6.0/fina/lcpt-fina.git</t>
+  </si>
+  <si>
+    <t>https://gitlab.hundsun.com/ifms6.0/fina/lcpt-web-manager-fina.git</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lcpt-web-manager-fina</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.hundsun.com/ifms6.0/fina/spsql-fina.git</t>
+  </si>
+  <si>
+    <t>spsql-fina</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.hundsun.com/ifms6.0/fina/sql-fina.git</t>
+  </si>
+  <si>
+    <t>sql-fina</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -302,7 +334,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -311,10 +343,19 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -337,10 +378,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -349,9 +391,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -367,9 +411,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -407,9 +451,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -442,26 +486,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -494,26 +521,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -688,15 +698,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B45"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="45.59765625" customWidth="1"/>
-    <col min="3" max="3" width="50.59765625" customWidth="1"/>
+    <col min="2" max="2" width="45.6640625" customWidth="1"/>
+    <col min="3" max="3" width="50.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -704,7 +714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -712,7 +722,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -720,7 +730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -728,7 +738,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -736,7 +746,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -744,7 +754,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -752,7 +762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -760,7 +770,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -768,7 +778,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -776,7 +786,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -784,7 +794,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -792,7 +802,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -800,7 +810,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -808,7 +818,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -816,7 +826,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -824,7 +834,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -832,7 +842,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -840,7 +850,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -848,7 +858,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
@@ -856,7 +866,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
@@ -864,7 +874,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -872,7 +882,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
@@ -880,7 +890,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -888,7 +898,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
         <v>48</v>
       </c>
@@ -896,7 +906,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
@@ -904,7 +914,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
         <v>52</v>
       </c>
@@ -912,7 +922,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -920,7 +930,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
         <v>56</v>
       </c>
@@ -928,7 +938,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
@@ -936,7 +946,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
         <v>60</v>
       </c>
@@ -944,7 +954,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
         <v>62</v>
       </c>
@@ -952,7 +962,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
         <v>64</v>
       </c>
@@ -960,7 +970,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
@@ -968,7 +978,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
         <v>68</v>
       </c>
@@ -976,7 +986,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
@@ -984,7 +994,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
         <v>72</v>
       </c>
@@ -992,7 +1002,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
@@ -1000,7 +1010,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
         <v>76</v>
       </c>
@@ -1008,7 +1018,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
         <v>77</v>
       </c>
@@ -1016,7 +1026,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
         <v>78</v>
       </c>
@@ -1024,7 +1034,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -1032,7 +1042,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2">
       <c r="A43" s="2" t="s">
         <v>87</v>
       </c>
@@ -1040,7 +1050,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2">
       <c r="A44" s="3" t="s">
         <v>88</v>
       </c>
@@ -1048,19 +1058,63 @@
         <v>85</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2">
       <c r="A45" s="3" t="s">
         <v>89</v>
       </c>
       <c r="B45" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:A38" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B46" r:id="rId1" xr:uid="{9D7CAB21-DFCE-5B4D-A1E3-AE81725FC25D}"/>
+    <hyperlink ref="B48" r:id="rId2" xr:uid="{F3F2DC47-D471-AF42-A681-D5B7FB25413D}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId3"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>